--- a/prep_and_checklists/JMAK  /ORDER_GUIDE_JMAK  _Tuesday, January 13, 2026  _0.xlsx
+++ b/prep_and_checklists/JMAK  /ORDER_GUIDE_JMAK  _Tuesday, January 13, 2026  _0.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/prep_and_checklists/JMAK  /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D62048A-2EB3-CB47-AD4C-2C6C158BDF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFEFC3F3-B361-9940-B137-50EDAD35552C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="1160" windowWidth="29940" windowHeight="17600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="300" yWindow="1220" windowWidth="29940" windowHeight="17600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="order_guide" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="104">
   <si>
     <t xml:space="preserve">Event:JMAK   Date: Tuesday, January 13, 2026   Guests:N/A  </t>
   </si>
@@ -326,6 +339,12 @@
   </si>
   <si>
     <t>4 DZ</t>
+  </si>
+  <si>
+    <t>*assorted whole fruits</t>
+  </si>
+  <si>
+    <t>1 case each?</t>
   </si>
 </sst>
 </file>
@@ -335,7 +354,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dddd\ m/d"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -384,6 +403,11 @@
     <font>
       <sz val="14"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -846,7 +870,7 @@
     <col min="9" max="9" width="24.6640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="22.33203125" style="2" customWidth="1"/>
     <col min="11" max="11" width="18.6640625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="27.5" style="2" customWidth="1"/>
     <col min="13" max="25" width="8.83203125" style="2" customWidth="1"/>
     <col min="26" max="26" width="14.5" style="2" customWidth="1"/>
     <col min="27" max="16384" width="14.5" style="2"/>
@@ -965,7 +989,7 @@
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
     </row>
-    <row r="4" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>85</v>
       </c>
@@ -1014,7 +1038,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
     </row>
-    <row r="5" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>15</v>
       </c>
@@ -1065,7 +1089,7 @@
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
     </row>
-    <row r="6" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>19</v>
       </c>
@@ -1116,7 +1140,7 @@
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
     </row>
-    <row r="7" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>25</v>
       </c>
@@ -1167,7 +1191,7 @@
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
     </row>
-    <row r="8" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>38</v>
       </c>
@@ -1216,7 +1240,7 @@
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
     </row>
-    <row r="9" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>42</v>
       </c>
@@ -1259,7 +1283,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>95</v>
       </c>
@@ -1300,7 +1324,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>51</v>
       </c>
@@ -1343,7 +1367,7 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
     </row>
-    <row r="12" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>53</v>
       </c>
@@ -1378,7 +1402,7 @@
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
     </row>
-    <row r="13" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>55</v>
       </c>
@@ -1413,7 +1437,7 @@
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
     </row>
-    <row r="14" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>57</v>
       </c>
@@ -1448,7 +1472,7 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
     </row>
-    <row r="15" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>59</v>
       </c>
@@ -1483,7 +1507,7 @@
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
     </row>
-    <row r="16" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>61</v>
       </c>
@@ -1518,7 +1542,7 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
     </row>
-    <row r="17" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>63</v>
       </c>
@@ -1553,7 +1577,7 @@
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
     </row>
-    <row r="18" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>65</v>
       </c>
@@ -1588,7 +1612,7 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
     </row>
-    <row r="19" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>67</v>
       </c>
@@ -1623,7 +1647,7 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
     </row>
-    <row r="20" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>69</v>
       </c>
@@ -1658,7 +1682,7 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
     </row>
-    <row r="21" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
         <v>71</v>
       </c>
@@ -1693,7 +1717,7 @@
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
     </row>
-    <row r="22" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>73</v>
       </c>
@@ -1728,7 +1752,7 @@
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
     </row>
-    <row r="23" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>91</v>
       </c>
@@ -1761,7 +1785,7 @@
       <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
     </row>
-    <row r="24" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>75</v>
       </c>
@@ -1796,7 +1820,7 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
     </row>
-    <row r="25" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
         <v>77</v>
       </c>
@@ -1831,7 +1855,7 @@
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
     </row>
-    <row r="26" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="18" t="s">
         <v>79</v>
       </c>
@@ -1866,7 +1890,7 @@
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
     </row>
-    <row r="27" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="27" t="s">
         <v>81</v>
       </c>
@@ -1901,19 +1925,25 @@
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
     </row>
-    <row r="28" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="24"/>
+    <row r="28" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28" s="28"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="29"/>
       <c r="M28" s="25"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -3491,7 +3521,8 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="I2:L2"/>
   </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="37" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="33" orientation="landscape"/>
 </worksheet>
 </file>